--- a/simpac/SIMPAC_JaDE_WBS.xlsx
+++ b/simpac/SIMPAC_JaDE_WBS.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="119">
   <si>
     <t>SIMPAC JaDE 법인통합 고도화 일정</t>
   </si>
@@ -165,15 +165,9 @@
     <t>서버 구축 · JaDE 4.0 세팅</t>
   </si>
   <si>
-    <t>서버/도메인 정보 제공 · 접속 환경 준비</t>
-  </si>
-  <si>
     <t>킥오프 · 수행계획 공유</t>
   </si>
   <si>
-    <t>담당자 지정 · 정기미팅 일정 확정</t>
-  </si>
-  <si>
     <t>09.07</t>
   </si>
   <si>
@@ -297,88 +291,96 @@
     <t>통합 로그인 테스트</t>
   </si>
   <si>
+    <t>기타 연동</t>
+  </si>
+  <si>
+    <t>10.19~11.20</t>
+  </si>
+  <si>
+    <t>API 연동</t>
+  </si>
+  <si>
+    <t>10.19~10.21</t>
+  </si>
+  <si>
+    <t>API 테스트</t>
+  </si>
+  <si>
+    <t>연동 결과 확인</t>
+  </si>
+  <si>
+    <t>10.26~10.30</t>
+  </si>
+  <si>
+    <t>출퇴근기록기 연동</t>
+  </si>
+  <si>
+    <t>11.02~11.13</t>
+  </si>
+  <si>
+    <t>출퇴근기록기 테스트</t>
+  </si>
+  <si>
+    <t>11.16~11.20</t>
+  </si>
+  <si>
+    <t>통합테스트 · 오픈</t>
+  </si>
+  <si>
+    <t>통합테스트 · 안정화</t>
+  </si>
+  <si>
+    <t>11.16~12.18</t>
+  </si>
+  <si>
+    <t>통합테스트</t>
+  </si>
+  <si>
+    <t>검수 시나리오 작성 · 테스트 수행 · 검수확인서 날인</t>
+  </si>
+  <si>
+    <t>11.16~11.27</t>
+  </si>
+  <si>
+    <t>시스템 오픈</t>
+  </si>
+  <si>
+    <t>임직원 공지 · 매뉴얼 배포</t>
+  </si>
+  <si>
+    <t>2026.11.30 오픈</t>
+  </si>
+  <si>
+    <t>안정화 지원</t>
+  </si>
+  <si>
+    <t>운영 이슈 접수 창구 운영</t>
+  </si>
+  <si>
+    <t>12.01~12.18</t>
+  </si>
+  <si>
+    <t>* 상기 일정은 사업 수행과정에서 협의에 따라 조정될 수 있습니다.</t>
+  </si>
+  <si>
+    <t>서버/도메인 정보 제공</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>담당자 지정 · 정기미팅 일정 · 오픈일정 확정</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
     <t>겸직자 대상 로그인 테스트 참여</t>
-  </si>
-  <si>
-    <t>기타 연동</t>
-  </si>
-  <si>
-    <t>10.19~11.20</t>
-  </si>
-  <si>
-    <t>API 연동</t>
-  </si>
-  <si>
-    <t>연동 대상 시스템 · 규격 확정</t>
-  </si>
-  <si>
-    <t>10.19~10.21</t>
-  </si>
-  <si>
-    <t>API 테스트</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>출퇴근 기록기 사번정보 변경</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>연동 결과 확인</t>
-  </si>
-  <si>
-    <t>10.26~10.30</t>
-  </si>
-  <si>
-    <t>출퇴근기록기 연동</t>
-  </si>
-  <si>
-    <t>기기 정보 및 설치 현황 제공</t>
-  </si>
-  <si>
-    <t>11.02~11.13</t>
-  </si>
-  <si>
-    <t>출퇴근기록기 테스트</t>
-  </si>
-  <si>
-    <t>현장 테스트 참여</t>
-  </si>
-  <si>
-    <t>11.16~11.20</t>
-  </si>
-  <si>
-    <t>통합테스트 · 오픈</t>
-  </si>
-  <si>
-    <t>통합테스트 · 안정화</t>
-  </si>
-  <si>
-    <t>11.16~12.18</t>
-  </si>
-  <si>
-    <t>통합테스트</t>
-  </si>
-  <si>
-    <t>검수 시나리오 작성 · 테스트 수행 · 검수확인서 날인</t>
-  </si>
-  <si>
-    <t>11.16~11.27</t>
-  </si>
-  <si>
-    <t>시스템 오픈</t>
-  </si>
-  <si>
-    <t>임직원 공지 · 매뉴얼 배포</t>
-  </si>
-  <si>
-    <t>2026.11.30 오픈</t>
-  </si>
-  <si>
-    <t>안정화 지원</t>
-  </si>
-  <si>
-    <t>운영 이슈 접수 창구 운영</t>
-  </si>
-  <si>
-    <t>12.01~12.18</t>
-  </si>
-  <si>
-    <t>* 상기 일정은 사업 수행과정에서 협의에 따라 조정될 수 있습니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -581,20 +583,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -909,27 +911,27 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -960,47 +962,47 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="20" t="s">
+      <c r="C9" s="21"/>
+      <c r="D9" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20" t="s">
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="20" t="s">
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="20" t="s">
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="R9" s="19"/>
-      <c r="S9" s="21" t="s">
+      <c r="R9" s="21"/>
+      <c r="S9" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="T9" s="21" t="s">
+      <c r="T9" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="28.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
@@ -1046,13 +1048,13 @@
       <c r="R10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
     </row>
     <row r="11" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
       <c r="D11" s="8" t="s">
         <v>29</v>
       </c>
@@ -1098,11 +1100,11 @@
       <c r="R11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
     </row>
     <row r="12" spans="1:20" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="22" t="s">
         <v>44</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -1130,7 +1132,7 @@
       </c>
     </row>
     <row r="13" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
+      <c r="A13" s="21"/>
       <c r="B13" s="12"/>
       <c r="C13" s="15" t="s">
         <v>47</v>
@@ -1151,17 +1153,17 @@
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
       <c r="S13" s="13" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="T13" s="14" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="19"/>
+      <c r="A14" s="21"/>
       <c r="B14" s="12"/>
       <c r="C14" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="12"/>
@@ -1179,18 +1181,18 @@
       <c r="Q14" s="12"/>
       <c r="R14" s="12"/>
       <c r="S14" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="T14" s="14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="T14" s="14" t="s">
+      <c r="B15" s="9" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>53</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="12"/>
@@ -1210,14 +1212,14 @@
       <c r="R15" s="12"/>
       <c r="S15" s="13"/>
       <c r="T15" s="14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19"/>
+      <c r="A16" s="21"/>
       <c r="B16" s="12"/>
       <c r="C16" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="16"/>
@@ -1236,14 +1238,14 @@
       <c r="R16" s="12"/>
       <c r="S16" s="13"/>
       <c r="T16" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
+      <c r="A17" s="21"/>
       <c r="B17" s="12"/>
       <c r="C17" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
@@ -1261,18 +1263,18 @@
       <c r="Q17" s="12"/>
       <c r="R17" s="12"/>
       <c r="S17" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="T17" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="T17" s="14" t="s">
+      <c r="B18" s="9" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>61</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="11"/>
@@ -1292,14 +1294,14 @@
       <c r="R18" s="12"/>
       <c r="S18" s="13"/>
       <c r="T18" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="12"/>
       <c r="C19" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
@@ -1317,17 +1319,17 @@
       <c r="Q19" s="12"/>
       <c r="R19" s="12"/>
       <c r="S19" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="19"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="12"/>
       <c r="C20" s="15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
@@ -1345,17 +1347,17 @@
       <c r="Q20" s="12"/>
       <c r="R20" s="12"/>
       <c r="S20" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="12"/>
       <c r="C21" s="15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
@@ -1373,17 +1375,17 @@
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
       <c r="S21" s="13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="19"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="12"/>
       <c r="C22" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
@@ -1401,17 +1403,17 @@
       <c r="Q22" s="12"/>
       <c r="R22" s="12"/>
       <c r="S22" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="12"/>
       <c r="C23" s="15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
@@ -1429,17 +1431,17 @@
       <c r="Q23" s="12"/>
       <c r="R23" s="12"/>
       <c r="S23" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="19"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="12"/>
       <c r="C24" s="15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
@@ -1457,17 +1459,17 @@
       <c r="Q24" s="12"/>
       <c r="R24" s="12"/>
       <c r="S24" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="12"/>
       <c r="C25" s="15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
@@ -1485,17 +1487,17 @@
       <c r="Q25" s="12"/>
       <c r="R25" s="12"/>
       <c r="S25" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="12"/>
       <c r="C26" s="15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="12"/>
@@ -1513,17 +1515,17 @@
       <c r="Q26" s="12"/>
       <c r="R26" s="12"/>
       <c r="S26" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="12"/>
       <c r="C27" s="15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
@@ -1541,18 +1543,18 @@
       <c r="Q27" s="12"/>
       <c r="R27" s="12"/>
       <c r="S27" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="T27" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="T27" s="14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
-        <v>87</v>
-      </c>
       <c r="B28" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="12"/>
@@ -1572,14 +1574,14 @@
       <c r="R28" s="12"/>
       <c r="S28" s="13"/>
       <c r="T28" s="14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="12"/>
       <c r="C29" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="12"/>
@@ -1597,17 +1599,17 @@
       <c r="Q29" s="12"/>
       <c r="R29" s="12"/>
       <c r="S29" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="19"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="12"/>
       <c r="C30" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="12"/>
@@ -1625,18 +1627,18 @@
       <c r="Q30" s="12"/>
       <c r="R30" s="12"/>
       <c r="S30" s="13" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
-        <v>93</v>
+      <c r="A31" s="22" t="s">
+        <v>90</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="12"/>
@@ -1656,14 +1658,14 @@
       <c r="R31" s="12"/>
       <c r="S31" s="13"/>
       <c r="T31" s="14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="19"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="12"/>
       <c r="C32" s="15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
@@ -1680,18 +1682,16 @@
       <c r="P32" s="12"/>
       <c r="Q32" s="12"/>
       <c r="R32" s="12"/>
-      <c r="S32" s="13" t="s">
-        <v>96</v>
-      </c>
+      <c r="S32" s="13"/>
       <c r="T32" s="14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="12"/>
       <c r="C33" s="15" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="12"/>
@@ -1709,17 +1709,17 @@
       <c r="Q33" s="12"/>
       <c r="R33" s="12"/>
       <c r="S33" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="19"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="12"/>
       <c r="C34" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="12"/>
@@ -1737,17 +1737,17 @@
       <c r="Q34" s="12"/>
       <c r="R34" s="12"/>
       <c r="S34" s="13" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="19"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="12"/>
       <c r="C35" s="15" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="12"/>
@@ -1765,18 +1765,18 @@
       <c r="Q35" s="12"/>
       <c r="R35" s="12"/>
       <c r="S35" s="13" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="18" t="s">
-        <v>107</v>
+      <c r="A36" s="22" t="s">
+        <v>101</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="12"/>
@@ -1796,14 +1796,14 @@
       <c r="R36" s="11"/>
       <c r="S36" s="13"/>
       <c r="T36" s="14" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="19"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="12"/>
       <c r="C37" s="15" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="12"/>
@@ -1821,17 +1821,17 @@
       <c r="Q37" s="12"/>
       <c r="R37" s="12"/>
       <c r="S37" s="13" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="19"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="12"/>
       <c r="C38" s="15" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="12"/>
@@ -1849,17 +1849,17 @@
       <c r="Q38" s="12"/>
       <c r="R38" s="12"/>
       <c r="S38" s="13" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="19"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="12"/>
       <c r="C39" s="15" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
@@ -1877,19 +1877,25 @@
       <c r="Q39" s="16"/>
       <c r="R39" s="16"/>
       <c r="S39" s="13" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="Q9:R9"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="A36:A39"/>
@@ -1899,12 +1905,6 @@
     <mergeCell ref="A31:A35"/>
     <mergeCell ref="A18:A27"/>
     <mergeCell ref="L9:P9"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="Q9:R9"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/simpac/SIMPAC_JaDE_WBS.xlsx
+++ b/simpac/SIMPAC_JaDE_WBS.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -88,8 +88,13 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +126,11 @@
         <fgColor rgb="FFE6E0ED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F81BD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -287,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -343,6 +353,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -708,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:T42"/>
+  <dimension ref="A2:T43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16.125" customWidth="1" style="19" min="1" max="1"/>
@@ -757,6 +770,14 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="33" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>정기미팅</t>
+        </is>
+      </c>
+    </row>
     <row r="8" ht="24" customHeight="1" s="19">
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -982,28 +1003,28 @@
       <c r="S11" s="30" t="n"/>
       <c r="T11" s="30" t="n"/>
     </row>
-    <row r="12" ht="22.15" customHeight="1" s="19">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>프로젝트 준비</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>프로젝트 준비 및 착수</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="11" t="n"/>
+    <row r="12" ht="19.95" customHeight="1" s="19">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>정기미팅</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>정기미팅</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="n"/>
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
+      <c r="G12" s="35" t="n"/>
       <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
+      <c r="I12" s="35" t="n"/>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
+      <c r="K12" s="35" t="n"/>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="M12" s="35" t="n"/>
       <c r="N12" s="12" t="n"/>
       <c r="O12" s="12" t="n"/>
       <c r="P12" s="12" t="n"/>
@@ -1012,19 +1033,23 @@
       <c r="S12" s="13" t="n"/>
       <c r="T12" s="14" t="inlineStr">
         <is>
-          <t>09.07~09.11</t>
+          <t>09.07 · 09.28 · 10.12 · 10.26 · 11.09 (월)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19.9" customHeight="1" s="19">
-      <c r="A13" s="27" t="n"/>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>서버 구축 · JaDE 4.0 세팅</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="n"/>
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>프로젝트 준비</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>프로젝트 준비 및 착수</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="11" t="n"/>
       <c r="E13" s="12" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
@@ -1039,11 +1064,7 @@
       <c r="P13" s="12" t="n"/>
       <c r="Q13" s="12" t="n"/>
       <c r="R13" s="12" t="n"/>
-      <c r="S13" s="13" t="inlineStr">
-        <is>
-          <t>서버/도메인 정보 제공</t>
-        </is>
-      </c>
+      <c r="S13" s="13" t="n"/>
       <c r="T13" s="14" t="inlineStr">
         <is>
           <t>09.07~09.11</t>
@@ -1051,11 +1072,11 @@
       </c>
     </row>
     <row r="14" ht="19.9" customHeight="1" s="19">
-      <c r="A14" s="30" t="n"/>
+      <c r="A14" s="27" t="n"/>
       <c r="B14" s="12" t="n"/>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>킥오프 · 수행계획 공유</t>
+          <t>서버 구축 · JaDE 4.0 세팅</t>
         </is>
       </c>
       <c r="D14" s="16" t="n"/>
@@ -1075,33 +1096,29 @@
       <c r="R14" s="12" t="n"/>
       <c r="S14" s="13" t="inlineStr">
         <is>
-          <t>담당자 지정 · 정기미팅 일정 · 오픈일정 확정</t>
+          <t>서버/도메인 정보 제공</t>
         </is>
       </c>
       <c r="T14" s="14" t="inlineStr">
         <is>
-          <t>09.07</t>
+          <t>09.07~09.11</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22.15" customHeight="1" s="19">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>소스전환</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>소스전환 (JaDE 3.0 → 4.0)</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>킥오프 · 수행계획 공유</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
@@ -1111,27 +1128,35 @@
       <c r="P15" s="12" t="n"/>
       <c r="Q15" s="12" t="n"/>
       <c r="R15" s="12" t="n"/>
-      <c r="S15" s="13" t="n"/>
+      <c r="S15" s="13" t="inlineStr">
+        <is>
+          <t>담당자 지정 · 정기미팅 일정 · 오픈일정 확정</t>
+        </is>
+      </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>09.14~10.16</t>
+          <t>09.07</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19.9" customHeight="1" s="19">
-      <c r="A16" s="27" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>JaDE 4.0 소스 전환</t>
-        </is>
-      </c>
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>소스전환</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>소스전환 (JaDE 3.0 → 4.0)</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n"/>
       <c r="D16" s="12" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
+      <c r="I16" s="11" t="n"/>
       <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
@@ -1144,24 +1169,24 @@
       <c r="S16" s="13" t="n"/>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>09.14~10.02</t>
+          <t>09.14~10.16</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19.9" customHeight="1" s="19">
-      <c r="A17" s="30" t="n"/>
+      <c r="A17" s="27" t="n"/>
       <c r="B17" s="12" t="n"/>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>전환 기능 검증</t>
+          <t>JaDE 4.0 소스 전환</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="17" t="n"/>
-      <c r="I17" s="17" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
@@ -1171,82 +1196,78 @@
       <c r="P17" s="12" t="n"/>
       <c r="Q17" s="12" t="n"/>
       <c r="R17" s="12" t="n"/>
-      <c r="S17" s="13" t="inlineStr">
-        <is>
-          <t>전환 기능 확인 및 결과 회신</t>
-        </is>
-      </c>
+      <c r="S17" s="13" t="n"/>
       <c r="T17" s="14" t="inlineStr">
         <is>
-          <t>10.06~10.16</t>
+          <t>09.14~10.02</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22.15" customHeight="1" s="19">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>데이터 이관</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>마이그레이션</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="11" t="n"/>
-      <c r="J18" s="11" t="n"/>
-      <c r="K18" s="11" t="n"/>
-      <c r="L18" s="11" t="n"/>
-      <c r="M18" s="11" t="n"/>
-      <c r="N18" s="11" t="n"/>
-      <c r="O18" s="11" t="n"/>
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>전환 기능 검증</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="17" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="12" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="12" t="n"/>
       <c r="P18" s="12" t="n"/>
       <c r="Q18" s="12" t="n"/>
       <c r="R18" s="12" t="n"/>
-      <c r="S18" s="13" t="n"/>
+      <c r="S18" s="13" t="inlineStr">
+        <is>
+          <t>전환 기능 확인 및 결과 회신</t>
+        </is>
+      </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>09.07~11.27</t>
+          <t>10.06~10.16</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19.9" customHeight="1" s="19">
-      <c r="A19" s="27" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>기초자료 점검 및 표준 수립</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="12" t="n"/>
-      <c r="O19" s="12" t="n"/>
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>데이터 이관</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>마이그레이션</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="11" t="n"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="11" t="n"/>
+      <c r="N19" s="11" t="n"/>
+      <c r="O19" s="11" t="n"/>
       <c r="P19" s="12" t="n"/>
       <c r="Q19" s="12" t="n"/>
       <c r="R19" s="12" t="n"/>
-      <c r="S19" s="13" t="inlineStr">
-        <is>
-          <t>중복 사번·조직·코드 변경안 확정 · 조직코드 표준정책 수립</t>
-        </is>
-      </c>
+      <c r="S19" s="13" t="n"/>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>09.07~09.18</t>
+          <t>09.07~11.27</t>
         </is>
       </c>
     </row>
@@ -1255,14 +1276,14 @@
       <c r="B20" s="12" t="n"/>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>인사/시스템 이관</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="16" t="n"/>
+          <t>기초자료 점검 및 표준 수립</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
@@ -1275,12 +1296,12 @@
       <c r="R20" s="12" t="n"/>
       <c r="S20" s="13" t="inlineStr">
         <is>
-          <t>이관 대상 범위 · 최종 반영 기준일 확정</t>
+          <t>중복 사번·조직·코드 변경안 확정 · 조직코드 표준정책 수립</t>
         </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
-          <t>09.21~10.08</t>
+          <t>09.07~09.18</t>
         </is>
       </c>
     </row>
@@ -1289,14 +1310,14 @@
       <c r="B21" s="12" t="n"/>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>· 데이터 점검 및 설정 통합</t>
+          <t>인사/시스템 이관</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
       <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="16" t="n"/>
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
@@ -1309,12 +1330,12 @@
       <c r="R21" s="12" t="n"/>
       <c r="S21" s="13" t="inlineStr">
         <is>
-          <t>법인별 설정 중복값 정비 · 이관 결과 검증</t>
+          <t>이관 대상 범위 · 최종 반영 기준일 확정</t>
         </is>
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
-          <t>09.28~10.08</t>
+          <t>09.21~10.08</t>
         </is>
       </c>
     </row>
@@ -1323,16 +1344,16 @@
       <c r="B22" s="12" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>근태 이관</t>
+          <t>· 데이터 점검 및 설정 통합</t>
         </is>
       </c>
       <c r="D22" s="12" t="n"/>
       <c r="E22" s="12" t="n"/>
       <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="16" t="n"/>
-      <c r="J22" s="16" t="n"/>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="12" t="n"/>
@@ -1343,12 +1364,12 @@
       <c r="R22" s="12" t="n"/>
       <c r="S22" s="13" t="inlineStr">
         <is>
-          <t>근태코드·근무유형·근로유형·근무조 정비안 확정</t>
+          <t>법인별 설정 중복값 정비 · 이관 결과 검증</t>
         </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>10.12~10.23</t>
+          <t>09.28~10.08</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1378,7 @@
       <c r="B23" s="12" t="n"/>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>· 데이터 점검 및 설정 통합</t>
+          <t>근태 이관</t>
         </is>
       </c>
       <c r="D23" s="12" t="n"/>
@@ -1365,8 +1386,8 @@
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="17" t="n"/>
+      <c r="I23" s="16" t="n"/>
+      <c r="J23" s="16" t="n"/>
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="12" t="n"/>
@@ -1377,12 +1398,12 @@
       <c r="R23" s="12" t="n"/>
       <c r="S23" s="13" t="inlineStr">
         <is>
-          <t>근태 기준 확인 · 이관 결과 검증</t>
+          <t>근태코드·근무유형·근로유형·근무조 정비안 확정</t>
         </is>
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>10.19~10.23</t>
+          <t>10.12~10.23</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1412,7 @@
       <c r="B24" s="12" t="n"/>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>급여/세무/정산 이관</t>
+          <t>· 데이터 점검 및 설정 통합</t>
         </is>
       </c>
       <c r="D24" s="12" t="n"/>
@@ -1400,9 +1421,9 @@
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
+      <c r="J24" s="17" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
       <c r="N24" s="12" t="n"/>
       <c r="O24" s="12" t="n"/>
@@ -1411,12 +1432,12 @@
       <c r="R24" s="12" t="n"/>
       <c r="S24" s="13" t="inlineStr">
         <is>
-          <t>급여항목·급여번호 정비안 확정</t>
+          <t>근태 기준 확인 · 이관 결과 검증</t>
         </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
         <is>
-          <t>10.26~11.06</t>
+          <t>10.19~10.23</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1446,7 @@
       <c r="B25" s="12" t="n"/>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>· 데이터 점검 및 설정 통합</t>
+          <t>급여/세무/정산 이관</t>
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
@@ -1435,8 +1456,8 @@
       <c r="H25" s="12" t="n"/>
       <c r="I25" s="12" t="n"/>
       <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="17" t="n"/>
+      <c r="K25" s="16" t="n"/>
+      <c r="L25" s="16" t="n"/>
       <c r="M25" s="12" t="n"/>
       <c r="N25" s="12" t="n"/>
       <c r="O25" s="12" t="n"/>
@@ -1445,12 +1466,12 @@
       <c r="R25" s="12" t="n"/>
       <c r="S25" s="13" t="inlineStr">
         <is>
-          <t>급여 기준 확인 · 이관 결과 검증</t>
+          <t>급여항목·급여번호 정비안 확정</t>
         </is>
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
-          <t>11.02~11.06</t>
+          <t>10.26~11.06</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1480,7 @@
       <c r="B26" s="12" t="n"/>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>교육/평가/신청/기타 이관</t>
+          <t>· 데이터 점검 및 설정 통합</t>
         </is>
       </c>
       <c r="D26" s="12" t="n"/>
@@ -1470,8 +1491,8 @@
       <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
       <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="16" t="n"/>
+      <c r="L26" s="17" t="n"/>
+      <c r="M26" s="12" t="n"/>
       <c r="N26" s="12" t="n"/>
       <c r="O26" s="12" t="n"/>
       <c r="P26" s="12" t="n"/>
@@ -1479,12 +1500,12 @@
       <c r="R26" s="12" t="n"/>
       <c r="S26" s="13" t="inlineStr">
         <is>
-          <t>신청유형 등 기타 중복코드 정비안 확정</t>
+          <t>급여 기준 확인 · 이관 결과 검증</t>
         </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>11.09~11.13</t>
+          <t>11.02~11.06</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1514,7 @@
       <c r="B27" s="12" t="n"/>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>· 데이터 점검 및 설정 통합</t>
+          <t>교육/평가/신청/기타 이관</t>
         </is>
       </c>
       <c r="D27" s="12" t="n"/>
@@ -1505,7 +1526,7 @@
       <c r="J27" s="12" t="n"/>
       <c r="K27" s="12" t="n"/>
       <c r="L27" s="12" t="n"/>
-      <c r="M27" s="17" t="n"/>
+      <c r="M27" s="16" t="n"/>
       <c r="N27" s="12" t="n"/>
       <c r="O27" s="12" t="n"/>
       <c r="P27" s="12" t="n"/>
@@ -1513,12 +1534,12 @@
       <c r="R27" s="12" t="n"/>
       <c r="S27" s="13" t="inlineStr">
         <is>
-          <t>이관 결과 검증</t>
+          <t>신청유형 등 기타 중복코드 정비안 확정</t>
         </is>
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
-          <t>11.11~11.13</t>
+          <t>11.09~11.13</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1548,7 @@
       <c r="B28" s="12" t="n"/>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>2차 운영 데이터 이관</t>
+          <t>· 데이터 점검 및 설정 통합</t>
         </is>
       </c>
       <c r="D28" s="12" t="n"/>
@@ -1539,93 +1560,93 @@
       <c r="J28" s="12" t="n"/>
       <c r="K28" s="12" t="n"/>
       <c r="L28" s="12" t="n"/>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="16" t="n"/>
-      <c r="O28" s="16" t="n"/>
+      <c r="M28" s="17" t="n"/>
+      <c r="N28" s="12" t="n"/>
+      <c r="O28" s="12" t="n"/>
       <c r="P28" s="12" t="n"/>
       <c r="Q28" s="12" t="n"/>
       <c r="R28" s="12" t="n"/>
-      <c r="S28" s="13" t="n"/>
+      <c r="S28" s="13" t="inlineStr">
+        <is>
+          <t>이관 결과 검증</t>
+        </is>
+      </c>
       <c r="T28" s="14" t="inlineStr">
         <is>
-          <t>11.16~11.27</t>
+          <t>11.11~11.13</t>
         </is>
       </c>
     </row>
     <row r="29" ht="19.9" customHeight="1" s="19">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>통합로그인</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>통합로그인</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="n"/>
+      <c r="A29" s="30" t="n"/>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>2차 운영 데이터 이관</t>
+        </is>
+      </c>
       <c r="D29" s="12" t="n"/>
       <c r="E29" s="12" t="n"/>
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="12" t="n"/>
       <c r="H29" s="12" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="11" t="n"/>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
       <c r="M29" s="12" t="n"/>
-      <c r="N29" s="12" t="n"/>
-      <c r="O29" s="12" t="n"/>
+      <c r="N29" s="16" t="n"/>
+      <c r="O29" s="16" t="n"/>
       <c r="P29" s="12" t="n"/>
       <c r="Q29" s="12" t="n"/>
       <c r="R29" s="12" t="n"/>
       <c r="S29" s="13" t="n"/>
       <c r="T29" s="14" t="inlineStr">
         <is>
-          <t>10.12~11.06</t>
+          <t>11.16~11.27</t>
         </is>
       </c>
     </row>
     <row r="30" ht="19.9" customHeight="1" s="19">
-      <c r="A30" s="27" t="n"/>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>SSO 및 다법인 겸직자 통합로그인 개발</t>
-        </is>
-      </c>
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>통합로그인</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>통합로그인</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n"/>
       <c r="D30" s="12" t="n"/>
       <c r="E30" s="12" t="n"/>
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="12" t="n"/>
       <c r="H30" s="12" t="n"/>
-      <c r="I30" s="16" t="n"/>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="12" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
       <c r="M30" s="12" t="n"/>
       <c r="N30" s="12" t="n"/>
       <c r="O30" s="12" t="n"/>
       <c r="P30" s="12" t="n"/>
       <c r="Q30" s="12" t="n"/>
       <c r="R30" s="12" t="n"/>
-      <c r="S30" s="13" t="inlineStr">
-        <is>
-          <t>겸직자 현황 · 로그인 정책 확정</t>
-        </is>
-      </c>
+      <c r="S30" s="13" t="n"/>
       <c r="T30" s="14" t="inlineStr">
         <is>
-          <t>10.12~10.23</t>
+          <t>10.12~11.06</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22.15" customHeight="1" s="19">
-      <c r="A31" s="30" t="n"/>
+      <c r="A31" s="27" t="n"/>
       <c r="B31" s="12" t="n"/>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>통합 로그인 테스트</t>
+          <t>SSO 및 다법인 겸직자 통합로그인 개발</t>
         </is>
       </c>
       <c r="D31" s="12" t="n"/>
@@ -1633,10 +1654,10 @@
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="12" t="n"/>
       <c r="H31" s="12" t="n"/>
-      <c r="I31" s="12" t="n"/>
-      <c r="J31" s="12" t="n"/>
-      <c r="K31" s="17" t="n"/>
-      <c r="L31" s="17" t="n"/>
+      <c r="I31" s="16" t="n"/>
+      <c r="J31" s="16" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
       <c r="M31" s="12" t="n"/>
       <c r="N31" s="12" t="n"/>
       <c r="O31" s="12" t="n"/>
@@ -1645,68 +1666,72 @@
       <c r="R31" s="12" t="n"/>
       <c r="S31" s="13" t="inlineStr">
         <is>
-          <t>겸직자 대상 로그인 테스트 참여</t>
+          <t>겸직자 현황 · 로그인 정책 확정</t>
         </is>
       </c>
       <c r="T31" s="14" t="inlineStr">
         <is>
-          <t>10.26~11.06</t>
+          <t>10.12~10.23</t>
         </is>
       </c>
     </row>
     <row r="32" ht="19.9" customHeight="1" s="19">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>기타 연동</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>기타 연동</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="n"/>
+      <c r="A32" s="30" t="n"/>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>통합 로그인 테스트</t>
+        </is>
+      </c>
       <c r="D32" s="12" t="n"/>
       <c r="E32" s="12" t="n"/>
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="12" t="n"/>
       <c r="H32" s="12" t="n"/>
       <c r="I32" s="12" t="n"/>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="11" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
-      <c r="N32" s="11" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="17" t="n"/>
+      <c r="L32" s="17" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
       <c r="O32" s="12" t="n"/>
       <c r="P32" s="12" t="n"/>
       <c r="Q32" s="12" t="n"/>
       <c r="R32" s="12" t="n"/>
-      <c r="S32" s="13" t="n"/>
+      <c r="S32" s="13" t="inlineStr">
+        <is>
+          <t>겸직자 대상 로그인 테스트 참여</t>
+        </is>
+      </c>
       <c r="T32" s="14" t="inlineStr">
         <is>
-          <t>10.19~11.20</t>
+          <t>10.26~11.06</t>
         </is>
       </c>
     </row>
     <row r="33" ht="19.9" customHeight="1" s="19">
-      <c r="A33" s="27" t="n"/>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>API 연동</t>
-        </is>
-      </c>
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>기타 연동</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>기타 연동</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n"/>
       <c r="D33" s="12" t="n"/>
       <c r="E33" s="12" t="n"/>
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="12" t="n"/>
       <c r="H33" s="12" t="n"/>
       <c r="I33" s="12" t="n"/>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="12" t="n"/>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="12" t="n"/>
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="11" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n"/>
+      <c r="N33" s="11" t="n"/>
       <c r="O33" s="12" t="n"/>
       <c r="P33" s="12" t="n"/>
       <c r="Q33" s="12" t="n"/>
@@ -1714,7 +1739,7 @@
       <c r="S33" s="13" t="n"/>
       <c r="T33" s="14" t="inlineStr">
         <is>
-          <t>10.19~10.21</t>
+          <t>10.19~11.20</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1748,7 @@
       <c r="B34" s="12" t="n"/>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>API 테스트</t>
+          <t>API 연동</t>
         </is>
       </c>
       <c r="D34" s="12" t="n"/>
@@ -1732,8 +1757,8 @@
       <c r="G34" s="12" t="n"/>
       <c r="H34" s="12" t="n"/>
       <c r="I34" s="12" t="n"/>
-      <c r="J34" s="12" t="n"/>
-      <c r="K34" s="17" t="n"/>
+      <c r="J34" s="16" t="n"/>
+      <c r="K34" s="12" t="n"/>
       <c r="L34" s="12" t="n"/>
       <c r="M34" s="12" t="n"/>
       <c r="N34" s="12" t="n"/>
@@ -1741,14 +1766,10 @@
       <c r="P34" s="12" t="n"/>
       <c r="Q34" s="12" t="n"/>
       <c r="R34" s="12" t="n"/>
-      <c r="S34" s="13" t="inlineStr">
-        <is>
-          <t>연동 결과 확인</t>
-        </is>
-      </c>
+      <c r="S34" s="13" t="n"/>
       <c r="T34" s="14" t="inlineStr">
         <is>
-          <t>10.26~10.30</t>
+          <t>10.19~10.21</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1778,7 @@
       <c r="B35" s="12" t="n"/>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>출퇴근기록기 연동</t>
+          <t>API 테스트</t>
         </is>
       </c>
       <c r="D35" s="12" t="n"/>
@@ -1767,9 +1788,9 @@
       <c r="H35" s="12" t="n"/>
       <c r="I35" s="12" t="n"/>
       <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="16" t="n"/>
-      <c r="M35" s="16" t="n"/>
+      <c r="K35" s="17" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="12" t="n"/>
       <c r="N35" s="12" t="n"/>
       <c r="O35" s="12" t="n"/>
       <c r="P35" s="12" t="n"/>
@@ -1777,21 +1798,21 @@
       <c r="R35" s="12" t="n"/>
       <c r="S35" s="13" t="inlineStr">
         <is>
-          <t>출퇴근 기록기 사번정보 변경</t>
+          <t>연동 결과 확인</t>
         </is>
       </c>
       <c r="T35" s="14" t="inlineStr">
         <is>
-          <t>11.02~11.13</t>
+          <t>10.26~10.30</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22.15" customHeight="1" s="19">
-      <c r="A36" s="30" t="n"/>
+      <c r="A36" s="27" t="n"/>
       <c r="B36" s="12" t="n"/>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>출퇴근기록기 테스트</t>
+          <t>출퇴근기록기 연동</t>
         </is>
       </c>
       <c r="D36" s="12" t="n"/>
@@ -1802,36 +1823,32 @@
       <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
       <c r="K36" s="12" t="n"/>
-      <c r="L36" s="12" t="n"/>
-      <c r="M36" s="12" t="n"/>
-      <c r="N36" s="17" t="n"/>
+      <c r="L36" s="16" t="n"/>
+      <c r="M36" s="16" t="n"/>
+      <c r="N36" s="12" t="n"/>
       <c r="O36" s="12" t="n"/>
       <c r="P36" s="12" t="n"/>
       <c r="Q36" s="12" t="n"/>
       <c r="R36" s="12" t="n"/>
       <c r="S36" s="13" t="inlineStr">
         <is>
-          <t>연동 결과 확인</t>
+          <t>출퇴근 기록기 사번정보 변경</t>
         </is>
       </c>
       <c r="T36" s="14" t="inlineStr">
         <is>
-          <t>11.16~11.20</t>
+          <t>11.02~11.13</t>
         </is>
       </c>
     </row>
     <row r="37" ht="19.9" customHeight="1" s="19">
-      <c r="A37" s="22" t="inlineStr">
-        <is>
-          <t>통합테스트 · 오픈</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>통합테스트 · 안정화</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="n"/>
+      <c r="A37" s="30" t="n"/>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>출퇴근기록기 테스트</t>
+        </is>
+      </c>
       <c r="D37" s="12" t="n"/>
       <c r="E37" s="12" t="n"/>
       <c r="F37" s="12" t="n"/>
@@ -1842,26 +1859,34 @@
       <c r="K37" s="12" t="n"/>
       <c r="L37" s="12" t="n"/>
       <c r="M37" s="12" t="n"/>
-      <c r="N37" s="11" t="n"/>
-      <c r="O37" s="11" t="n"/>
-      <c r="P37" s="11" t="n"/>
-      <c r="Q37" s="11" t="n"/>
-      <c r="R37" s="11" t="n"/>
-      <c r="S37" s="13" t="n"/>
+      <c r="N37" s="17" t="n"/>
+      <c r="O37" s="12" t="n"/>
+      <c r="P37" s="12" t="n"/>
+      <c r="Q37" s="12" t="n"/>
+      <c r="R37" s="12" t="n"/>
+      <c r="S37" s="13" t="inlineStr">
+        <is>
+          <t>연동 결과 확인</t>
+        </is>
+      </c>
       <c r="T37" s="14" t="inlineStr">
         <is>
-          <t>11.16~12.18</t>
+          <t>11.16~11.20</t>
         </is>
       </c>
     </row>
     <row r="38" ht="19.9" customHeight="1" s="19">
-      <c r="A38" s="27" t="n"/>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>통합테스트</t>
-        </is>
-      </c>
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>통합테스트 · 오픈</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>통합테스트 · 안정화</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="n"/>
       <c r="D38" s="12" t="n"/>
       <c r="E38" s="12" t="n"/>
       <c r="F38" s="12" t="n"/>
@@ -1872,19 +1897,15 @@
       <c r="K38" s="12" t="n"/>
       <c r="L38" s="12" t="n"/>
       <c r="M38" s="12" t="n"/>
-      <c r="N38" s="17" t="n"/>
-      <c r="O38" s="17" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="12" t="n"/>
-      <c r="R38" s="12" t="n"/>
-      <c r="S38" s="13" t="inlineStr">
-        <is>
-          <t>검수 시나리오 작성 · 테스트 수행 · 검수확인서 날인</t>
-        </is>
-      </c>
+      <c r="N38" s="11" t="n"/>
+      <c r="O38" s="11" t="n"/>
+      <c r="P38" s="11" t="n"/>
+      <c r="Q38" s="11" t="n"/>
+      <c r="R38" s="11" t="n"/>
+      <c r="S38" s="13" t="n"/>
       <c r="T38" s="14" t="inlineStr">
         <is>
-          <t>11.16~11.27</t>
+          <t>11.16~12.18</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1914,7 @@
       <c r="B39" s="12" t="n"/>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>시스템 오픈</t>
+          <t>통합테스트</t>
         </is>
       </c>
       <c r="D39" s="12" t="n"/>
@@ -1906,28 +1927,28 @@
       <c r="K39" s="12" t="n"/>
       <c r="L39" s="12" t="n"/>
       <c r="M39" s="12" t="n"/>
-      <c r="N39" s="12" t="n"/>
-      <c r="O39" s="12" t="n"/>
-      <c r="P39" s="16" t="n"/>
+      <c r="N39" s="17" t="n"/>
+      <c r="O39" s="17" t="n"/>
+      <c r="P39" s="12" t="n"/>
       <c r="Q39" s="12" t="n"/>
       <c r="R39" s="12" t="n"/>
       <c r="S39" s="13" t="inlineStr">
         <is>
-          <t>임직원 공지 · 매뉴얼 배포</t>
+          <t>검수 시나리오 작성 · 테스트 수행 · 검수확인서 날인</t>
         </is>
       </c>
       <c r="T39" s="14" t="inlineStr">
         <is>
-          <t>2026.11.30 오픈</t>
+          <t>11.16~11.27</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="n"/>
+      <c r="A40" s="27" t="n"/>
       <c r="B40" s="12" t="n"/>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>안정화 지원</t>
+          <t>시스템 오픈</t>
         </is>
       </c>
       <c r="D40" s="12" t="n"/>
@@ -1943,21 +1964,56 @@
       <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="16" t="n"/>
-      <c r="Q40" s="16" t="n"/>
-      <c r="R40" s="16" t="n"/>
+      <c r="Q40" s="12" t="n"/>
+      <c r="R40" s="12" t="n"/>
       <c r="S40" s="13" t="inlineStr">
         <is>
+          <t>임직원 공지 · 매뉴얼 배포</t>
+        </is>
+      </c>
+      <c r="T40" s="14" t="inlineStr">
+        <is>
+          <t>2026.11.30 오픈</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="n"/>
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>안정화 지원</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="12" t="n"/>
+      <c r="G41" s="12" t="n"/>
+      <c r="H41" s="12" t="n"/>
+      <c r="I41" s="12" t="n"/>
+      <c r="J41" s="12" t="n"/>
+      <c r="K41" s="12" t="n"/>
+      <c r="L41" s="12" t="n"/>
+      <c r="M41" s="12" t="n"/>
+      <c r="N41" s="12" t="n"/>
+      <c r="O41" s="12" t="n"/>
+      <c r="P41" s="16" t="n"/>
+      <c r="Q41" s="16" t="n"/>
+      <c r="R41" s="16" t="n"/>
+      <c r="S41" s="13" t="inlineStr">
+        <is>
           <t>운영 이슈 접수 창구 운영</t>
         </is>
       </c>
-      <c r="T40" s="14" t="inlineStr">
+      <c r="T41" s="14" t="inlineStr">
         <is>
           <t>12.01~12.18</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>* 상기 일정은 사업 수행과정에서 협의에 따라 조정될 수 있습니다.</t>
         </is>
@@ -1965,19 +2021,19 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="A19:A29"/>
+    <mergeCell ref="A13:A15"/>
     <mergeCell ref="L9:P9"/>
     <mergeCell ref="T9:T11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="A18:A28"/>
-    <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A38:A41"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A9:A11"/>
   </mergeCells>

--- a/simpac/SIMPAC_JaDE_WBS.xlsx
+++ b/simpac/SIMPAC_JaDE_WBS.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -88,13 +88,8 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -126,11 +121,6 @@
         <fgColor rgb="FFE6E0ED"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004F81BD"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -297,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -353,9 +343,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -721,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:T43"/>
+  <dimension ref="A2:T42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16.125" customWidth="1" style="19" min="1" max="1"/>
@@ -770,14 +757,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="33" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>정기미팅</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="24" customHeight="1" s="19">
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -1003,28 +982,28 @@
       <c r="S11" s="30" t="n"/>
       <c r="T11" s="30" t="n"/>
     </row>
-    <row r="12" ht="19.95" customHeight="1" s="19">
-      <c r="A12" s="34" t="inlineStr">
-        <is>
-          <t>정기미팅</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>정기미팅</t>
-        </is>
-      </c>
-      <c r="D12" s="35" t="n"/>
+    <row r="12" ht="22.15" customHeight="1" s="19">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>프로젝트 준비</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>프로젝트 준비 및 착수</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="11" t="n"/>
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="12" t="n"/>
-      <c r="G12" s="35" t="n"/>
+      <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
-      <c r="I12" s="35" t="n"/>
+      <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="35" t="n"/>
+      <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="35" t="n"/>
+      <c r="M12" s="12" t="n"/>
       <c r="N12" s="12" t="n"/>
       <c r="O12" s="12" t="n"/>
       <c r="P12" s="12" t="n"/>
@@ -1033,23 +1012,19 @@
       <c r="S12" s="13" t="n"/>
       <c r="T12" s="14" t="inlineStr">
         <is>
-          <t>09.07 · 09.28 · 10.12 · 10.26 · 11.09 (월)</t>
+          <t>09.07~09.11</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19.9" customHeight="1" s="19">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>프로젝트 준비</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>프로젝트 준비 및 착수</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="11" t="n"/>
+      <c r="A13" s="27" t="n"/>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>서버 구축 · JaDE 4.0 세팅</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="n"/>
       <c r="E13" s="12" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
@@ -1064,7 +1039,11 @@
       <c r="P13" s="12" t="n"/>
       <c r="Q13" s="12" t="n"/>
       <c r="R13" s="12" t="n"/>
-      <c r="S13" s="13" t="n"/>
+      <c r="S13" s="13" t="inlineStr">
+        <is>
+          <t>서버/도메인 정보 제공</t>
+        </is>
+      </c>
       <c r="T13" s="14" t="inlineStr">
         <is>
           <t>09.07~09.11</t>
@@ -1072,11 +1051,11 @@
       </c>
     </row>
     <row r="14" ht="19.9" customHeight="1" s="19">
-      <c r="A14" s="27" t="n"/>
+      <c r="A14" s="30" t="n"/>
       <c r="B14" s="12" t="n"/>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>서버 구축 · JaDE 4.0 세팅</t>
+          <t>킥오프 · 수행계획 공유</t>
         </is>
       </c>
       <c r="D14" s="16" t="n"/>
@@ -1096,29 +1075,33 @@
       <c r="R14" s="12" t="n"/>
       <c r="S14" s="13" t="inlineStr">
         <is>
-          <t>서버/도메인 정보 제공</t>
+          <t>담당자 지정 · 정기미팅 일정 · 오픈일정 확정</t>
         </is>
       </c>
       <c r="T14" s="14" t="inlineStr">
         <is>
-          <t>09.07~09.11</t>
+          <t>09.07</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22.15" customHeight="1" s="19">
-      <c r="A15" s="30" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>킥오프 · 수행계획 공유</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>소스전환</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>소스전환 (JaDE 3.0 → 4.0)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
@@ -1128,35 +1111,27 @@
       <c r="P15" s="12" t="n"/>
       <c r="Q15" s="12" t="n"/>
       <c r="R15" s="12" t="n"/>
-      <c r="S15" s="13" t="inlineStr">
-        <is>
-          <t>담당자 지정 · 정기미팅 일정 · 오픈일정 확정</t>
-        </is>
-      </c>
+      <c r="S15" s="13" t="n"/>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>09.07</t>
+          <t>09.14~10.16</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19.9" customHeight="1" s="19">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>소스전환</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>소스전환 (JaDE 3.0 → 4.0)</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="n"/>
+      <c r="A16" s="27" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>JaDE 4.0 소스 전환</t>
+        </is>
+      </c>
       <c r="D16" s="12" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
-      <c r="I16" s="11" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
@@ -1169,24 +1144,24 @@
       <c r="S16" s="13" t="n"/>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>09.14~10.16</t>
+          <t>09.14~10.02</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19.9" customHeight="1" s="19">
-      <c r="A17" s="27" t="n"/>
+      <c r="A17" s="30" t="n"/>
       <c r="B17" s="12" t="n"/>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>JaDE 4.0 소스 전환</t>
+          <t>전환 기능 검증</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="17" t="n"/>
+      <c r="I17" s="17" t="n"/>
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
@@ -1196,78 +1171,82 @@
       <c r="P17" s="12" t="n"/>
       <c r="Q17" s="12" t="n"/>
       <c r="R17" s="12" t="n"/>
-      <c r="S17" s="13" t="n"/>
+      <c r="S17" s="13" t="inlineStr">
+        <is>
+          <t>전환 기능 확인 및 결과 회신</t>
+        </is>
+      </c>
       <c r="T17" s="14" t="inlineStr">
         <is>
-          <t>09.14~10.02</t>
+          <t>10.06~10.16</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22.15" customHeight="1" s="19">
-      <c r="A18" s="30" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>전환 기능 검증</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="17" t="n"/>
-      <c r="I18" s="17" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n"/>
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>데이터 이관</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>마이그레이션</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="11" t="n"/>
+      <c r="L18" s="11" t="n"/>
+      <c r="M18" s="11" t="n"/>
+      <c r="N18" s="11" t="n"/>
+      <c r="O18" s="11" t="n"/>
       <c r="P18" s="12" t="n"/>
       <c r="Q18" s="12" t="n"/>
       <c r="R18" s="12" t="n"/>
-      <c r="S18" s="13" t="inlineStr">
-        <is>
-          <t>전환 기능 확인 및 결과 회신</t>
-        </is>
-      </c>
+      <c r="S18" s="13" t="n"/>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>10.06~10.16</t>
+          <t>09.07~11.27</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19.9" customHeight="1" s="19">
-      <c r="A19" s="22" t="inlineStr">
-        <is>
-          <t>데이터 이관</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>마이그레이션</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="11" t="n"/>
-      <c r="K19" s="11" t="n"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11" t="n"/>
+      <c r="A19" s="27" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>기초자료 점검 및 표준 수립</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="12" t="n"/>
       <c r="P19" s="12" t="n"/>
       <c r="Q19" s="12" t="n"/>
       <c r="R19" s="12" t="n"/>
-      <c r="S19" s="13" t="n"/>
+      <c r="S19" s="13" t="inlineStr">
+        <is>
+          <t>중복 사번·조직·코드 변경안 확정 · 조직코드 표준정책 수립</t>
+        </is>
+      </c>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>09.07~11.27</t>
+          <t>09.07~09.18</t>
         </is>
       </c>
     </row>
@@ -1276,14 +1255,14 @@
       <c r="B20" s="12" t="n"/>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>기초자료 점검 및 표준 수립</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
+          <t>인사/시스템 이관</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="16" t="n"/>
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
@@ -1296,12 +1275,12 @@
       <c r="R20" s="12" t="n"/>
       <c r="S20" s="13" t="inlineStr">
         <is>
-          <t>중복 사번·조직·코드 변경안 확정 · 조직코드 표준정책 수립</t>
+          <t>이관 대상 범위 · 최종 반영 기준일 확정</t>
         </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
-          <t>09.07~09.18</t>
+          <t>09.21~10.08</t>
         </is>
       </c>
     </row>
@@ -1310,14 +1289,14 @@
       <c r="B21" s="12" t="n"/>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>인사/시스템 이관</t>
+          <t>· 데이터 점검 및 설정 통합</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
       <c r="E21" s="12" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="16" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="n"/>
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
@@ -1330,12 +1309,12 @@
       <c r="R21" s="12" t="n"/>
       <c r="S21" s="13" t="inlineStr">
         <is>
-          <t>이관 대상 범위 · 최종 반영 기준일 확정</t>
+          <t>법인별 설정 중복값 정비 · 이관 결과 검증</t>
         </is>
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
-          <t>09.21~10.08</t>
+          <t>09.28~10.08</t>
         </is>
       </c>
     </row>
@@ -1344,16 +1323,16 @@
       <c r="B22" s="12" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>· 데이터 점검 및 설정 통합</t>
+          <t>근태 이관</t>
         </is>
       </c>
       <c r="D22" s="12" t="n"/>
       <c r="E22" s="12" t="n"/>
       <c r="F22" s="12" t="n"/>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="n"/>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="16" t="n"/>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="12" t="n"/>
@@ -1364,12 +1343,12 @@
       <c r="R22" s="12" t="n"/>
       <c r="S22" s="13" t="inlineStr">
         <is>
-          <t>법인별 설정 중복값 정비 · 이관 결과 검증</t>
+          <t>근태코드·근무유형·근로유형·근무조 정비안 확정</t>
         </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>09.28~10.08</t>
+          <t>10.12~10.23</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1357,7 @@
       <c r="B23" s="12" t="n"/>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>근태 이관</t>
+          <t>· 데이터 점검 및 설정 통합</t>
         </is>
       </c>
       <c r="D23" s="12" t="n"/>
@@ -1386,8 +1365,8 @@
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
-      <c r="I23" s="16" t="n"/>
-      <c r="J23" s="16" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="17" t="n"/>
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="12" t="n"/>
@@ -1398,12 +1377,12 @@
       <c r="R23" s="12" t="n"/>
       <c r="S23" s="13" t="inlineStr">
         <is>
-          <t>근태코드·근무유형·근로유형·근무조 정비안 확정</t>
+          <t>근태 기준 확인 · 이관 결과 검증</t>
         </is>
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>10.12~10.23</t>
+          <t>10.19~10.23</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1391,7 @@
       <c r="B24" s="12" t="n"/>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>· 데이터 점검 및 설정 통합</t>
+          <t>급여/세무/정산 이관</t>
         </is>
       </c>
       <c r="D24" s="12" t="n"/>
@@ -1421,9 +1400,9 @@
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n"/>
-      <c r="J24" s="17" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="16" t="n"/>
+      <c r="L24" s="16" t="n"/>
       <c r="M24" s="12" t="n"/>
       <c r="N24" s="12" t="n"/>
       <c r="O24" s="12" t="n"/>
@@ -1432,12 +1411,12 @@
       <c r="R24" s="12" t="n"/>
       <c r="S24" s="13" t="inlineStr">
         <is>
-          <t>근태 기준 확인 · 이관 결과 검증</t>
+          <t>급여항목·급여번호 정비안 확정</t>
         </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
         <is>
-          <t>10.19~10.23</t>
+          <t>10.26~11.06</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1425,7 @@
       <c r="B25" s="12" t="n"/>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>급여/세무/정산 이관</t>
+          <t>· 데이터 점검 및 설정 통합</t>
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
@@ -1456,8 +1435,8 @@
       <c r="H25" s="12" t="n"/>
       <c r="I25" s="12" t="n"/>
       <c r="J25" s="12" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="17" t="n"/>
       <c r="M25" s="12" t="n"/>
       <c r="N25" s="12" t="n"/>
       <c r="O25" s="12" t="n"/>
@@ -1466,12 +1445,12 @@
       <c r="R25" s="12" t="n"/>
       <c r="S25" s="13" t="inlineStr">
         <is>
-          <t>급여항목·급여번호 정비안 확정</t>
+          <t>급여 기준 확인 · 이관 결과 검증</t>
         </is>
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
-          <t>10.26~11.06</t>
+          <t>11.02~11.06</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1459,7 @@
       <c r="B26" s="12" t="n"/>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>· 데이터 점검 및 설정 통합</t>
+          <t>교육/평가/신청/기타 이관</t>
         </is>
       </c>
       <c r="D26" s="12" t="n"/>
@@ -1491,8 +1470,8 @@
       <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
       <c r="K26" s="12" t="n"/>
-      <c r="L26" s="17" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="16" t="n"/>
       <c r="N26" s="12" t="n"/>
       <c r="O26" s="12" t="n"/>
       <c r="P26" s="12" t="n"/>
@@ -1500,12 +1479,12 @@
       <c r="R26" s="12" t="n"/>
       <c r="S26" s="13" t="inlineStr">
         <is>
-          <t>급여 기준 확인 · 이관 결과 검증</t>
+          <t>신청유형 등 기타 중복코드 정비안 확정</t>
         </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>11.02~11.06</t>
+          <t>11.09~11.13</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1493,7 @@
       <c r="B27" s="12" t="n"/>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>교육/평가/신청/기타 이관</t>
+          <t>· 데이터 점검 및 설정 통합</t>
         </is>
       </c>
       <c r="D27" s="12" t="n"/>
@@ -1526,7 +1505,7 @@
       <c r="J27" s="12" t="n"/>
       <c r="K27" s="12" t="n"/>
       <c r="L27" s="12" t="n"/>
-      <c r="M27" s="16" t="n"/>
+      <c r="M27" s="17" t="n"/>
       <c r="N27" s="12" t="n"/>
       <c r="O27" s="12" t="n"/>
       <c r="P27" s="12" t="n"/>
@@ -1534,12 +1513,12 @@
       <c r="R27" s="12" t="n"/>
       <c r="S27" s="13" t="inlineStr">
         <is>
-          <t>신청유형 등 기타 중복코드 정비안 확정</t>
+          <t>이관 결과 검증</t>
         </is>
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
-          <t>11.09~11.13</t>
+          <t>11.11~11.13</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1527,7 @@
       <c r="B28" s="12" t="n"/>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>· 데이터 점검 및 설정 통합</t>
+          <t>2차 운영 데이터 이관</t>
         </is>
       </c>
       <c r="D28" s="12" t="n"/>
@@ -1560,93 +1539,93 @@
       <c r="J28" s="12" t="n"/>
       <c r="K28" s="12" t="n"/>
       <c r="L28" s="12" t="n"/>
-      <c r="M28" s="17" t="n"/>
-      <c r="N28" s="12" t="n"/>
-      <c r="O28" s="12" t="n"/>
+      <c r="M28" s="12" t="n"/>
+      <c r="N28" s="16" t="n"/>
+      <c r="O28" s="16" t="n"/>
       <c r="P28" s="12" t="n"/>
       <c r="Q28" s="12" t="n"/>
       <c r="R28" s="12" t="n"/>
-      <c r="S28" s="13" t="inlineStr">
-        <is>
-          <t>이관 결과 검증</t>
-        </is>
-      </c>
+      <c r="S28" s="13" t="n"/>
       <c r="T28" s="14" t="inlineStr">
         <is>
-          <t>11.11~11.13</t>
+          <t>11.16~11.27</t>
         </is>
       </c>
     </row>
     <row r="29" ht="19.9" customHeight="1" s="19">
-      <c r="A29" s="30" t="n"/>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>2차 운영 데이터 이관</t>
-        </is>
-      </c>
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>통합로그인</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>통합로그인</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="n"/>
       <c r="D29" s="12" t="n"/>
       <c r="E29" s="12" t="n"/>
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="12" t="n"/>
       <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="12" t="n"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="11" t="n"/>
       <c r="M29" s="12" t="n"/>
-      <c r="N29" s="16" t="n"/>
-      <c r="O29" s="16" t="n"/>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="12" t="n"/>
       <c r="P29" s="12" t="n"/>
       <c r="Q29" s="12" t="n"/>
       <c r="R29" s="12" t="n"/>
       <c r="S29" s="13" t="n"/>
       <c r="T29" s="14" t="inlineStr">
         <is>
-          <t>11.16~11.27</t>
+          <t>10.12~11.06</t>
         </is>
       </c>
     </row>
     <row r="30" ht="19.9" customHeight="1" s="19">
-      <c r="A30" s="22" t="inlineStr">
-        <is>
-          <t>통합로그인</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>통합로그인</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="n"/>
+      <c r="A30" s="27" t="n"/>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>SSO 및 다법인 겸직자 통합로그인 개발</t>
+        </is>
+      </c>
       <c r="D30" s="12" t="n"/>
       <c r="E30" s="12" t="n"/>
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="12" t="n"/>
       <c r="H30" s="12" t="n"/>
-      <c r="I30" s="11" t="n"/>
-      <c r="J30" s="11" t="n"/>
-      <c r="K30" s="11" t="n"/>
-      <c r="L30" s="11" t="n"/>
+      <c r="I30" s="16" t="n"/>
+      <c r="J30" s="16" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
       <c r="M30" s="12" t="n"/>
       <c r="N30" s="12" t="n"/>
       <c r="O30" s="12" t="n"/>
       <c r="P30" s="12" t="n"/>
       <c r="Q30" s="12" t="n"/>
       <c r="R30" s="12" t="n"/>
-      <c r="S30" s="13" t="n"/>
+      <c r="S30" s="13" t="inlineStr">
+        <is>
+          <t>겸직자 현황 · 로그인 정책 확정</t>
+        </is>
+      </c>
       <c r="T30" s="14" t="inlineStr">
         <is>
-          <t>10.12~11.06</t>
+          <t>10.12~10.23</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22.15" customHeight="1" s="19">
-      <c r="A31" s="27" t="n"/>
+      <c r="A31" s="30" t="n"/>
       <c r="B31" s="12" t="n"/>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>SSO 및 다법인 겸직자 통합로그인 개발</t>
+          <t>통합 로그인 테스트</t>
         </is>
       </c>
       <c r="D31" s="12" t="n"/>
@@ -1654,10 +1633,10 @@
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="12" t="n"/>
       <c r="H31" s="12" t="n"/>
-      <c r="I31" s="16" t="n"/>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="17" t="n"/>
+      <c r="L31" s="17" t="n"/>
       <c r="M31" s="12" t="n"/>
       <c r="N31" s="12" t="n"/>
       <c r="O31" s="12" t="n"/>
@@ -1666,72 +1645,68 @@
       <c r="R31" s="12" t="n"/>
       <c r="S31" s="13" t="inlineStr">
         <is>
-          <t>겸직자 현황 · 로그인 정책 확정</t>
+          <t>겸직자 대상 로그인 테스트 참여</t>
         </is>
       </c>
       <c r="T31" s="14" t="inlineStr">
         <is>
-          <t>10.12~10.23</t>
+          <t>10.26~11.06</t>
         </is>
       </c>
     </row>
     <row r="32" ht="19.9" customHeight="1" s="19">
-      <c r="A32" s="30" t="n"/>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>통합 로그인 테스트</t>
-        </is>
-      </c>
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>기타 연동</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>기타 연동</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n"/>
       <c r="D32" s="12" t="n"/>
       <c r="E32" s="12" t="n"/>
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="12" t="n"/>
       <c r="H32" s="12" t="n"/>
       <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="17" t="n"/>
-      <c r="L32" s="17" t="n"/>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="12" t="n"/>
+      <c r="J32" s="11" t="n"/>
+      <c r="K32" s="11" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="11" t="n"/>
+      <c r="N32" s="11" t="n"/>
       <c r="O32" s="12" t="n"/>
       <c r="P32" s="12" t="n"/>
       <c r="Q32" s="12" t="n"/>
       <c r="R32" s="12" t="n"/>
-      <c r="S32" s="13" t="inlineStr">
-        <is>
-          <t>겸직자 대상 로그인 테스트 참여</t>
-        </is>
-      </c>
+      <c r="S32" s="13" t="n"/>
       <c r="T32" s="14" t="inlineStr">
         <is>
-          <t>10.26~11.06</t>
+          <t>10.19~11.20</t>
         </is>
       </c>
     </row>
     <row r="33" ht="19.9" customHeight="1" s="19">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>기타 연동</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>기타 연동</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="n"/>
+      <c r="A33" s="27" t="n"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>API 연동</t>
+        </is>
+      </c>
       <c r="D33" s="12" t="n"/>
       <c r="E33" s="12" t="n"/>
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="12" t="n"/>
       <c r="H33" s="12" t="n"/>
       <c r="I33" s="12" t="n"/>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="11" t="n"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="11" t="n"/>
+      <c r="J33" s="16" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+      <c r="N33" s="12" t="n"/>
       <c r="O33" s="12" t="n"/>
       <c r="P33" s="12" t="n"/>
       <c r="Q33" s="12" t="n"/>
@@ -1739,7 +1714,7 @@
       <c r="S33" s="13" t="n"/>
       <c r="T33" s="14" t="inlineStr">
         <is>
-          <t>10.19~11.20</t>
+          <t>10.19~10.21</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1723,7 @@
       <c r="B34" s="12" t="n"/>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>API 연동</t>
+          <t>API 테스트</t>
         </is>
       </c>
       <c r="D34" s="12" t="n"/>
@@ -1757,8 +1732,8 @@
       <c r="G34" s="12" t="n"/>
       <c r="H34" s="12" t="n"/>
       <c r="I34" s="12" t="n"/>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="17" t="n"/>
       <c r="L34" s="12" t="n"/>
       <c r="M34" s="12" t="n"/>
       <c r="N34" s="12" t="n"/>
@@ -1766,10 +1741,14 @@
       <c r="P34" s="12" t="n"/>
       <c r="Q34" s="12" t="n"/>
       <c r="R34" s="12" t="n"/>
-      <c r="S34" s="13" t="n"/>
+      <c r="S34" s="13" t="inlineStr">
+        <is>
+          <t>연동 결과 확인</t>
+        </is>
+      </c>
       <c r="T34" s="14" t="inlineStr">
         <is>
-          <t>10.19~10.21</t>
+          <t>10.26~10.30</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1757,7 @@
       <c r="B35" s="12" t="n"/>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>API 테스트</t>
+          <t>출퇴근기록기 연동</t>
         </is>
       </c>
       <c r="D35" s="12" t="n"/>
@@ -1788,9 +1767,9 @@
       <c r="H35" s="12" t="n"/>
       <c r="I35" s="12" t="n"/>
       <c r="J35" s="12" t="n"/>
-      <c r="K35" s="17" t="n"/>
-      <c r="L35" s="12" t="n"/>
-      <c r="M35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="16" t="n"/>
+      <c r="M35" s="16" t="n"/>
       <c r="N35" s="12" t="n"/>
       <c r="O35" s="12" t="n"/>
       <c r="P35" s="12" t="n"/>
@@ -1798,21 +1777,21 @@
       <c r="R35" s="12" t="n"/>
       <c r="S35" s="13" t="inlineStr">
         <is>
-          <t>연동 결과 확인</t>
+          <t>출퇴근 기록기 사번정보 변경</t>
         </is>
       </c>
       <c r="T35" s="14" t="inlineStr">
         <is>
-          <t>10.26~10.30</t>
+          <t>11.02~11.13</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22.15" customHeight="1" s="19">
-      <c r="A36" s="27" t="n"/>
+      <c r="A36" s="30" t="n"/>
       <c r="B36" s="12" t="n"/>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>출퇴근기록기 연동</t>
+          <t>출퇴근기록기 테스트</t>
         </is>
       </c>
       <c r="D36" s="12" t="n"/>
@@ -1823,32 +1802,36 @@
       <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
       <c r="K36" s="12" t="n"/>
-      <c r="L36" s="16" t="n"/>
-      <c r="M36" s="16" t="n"/>
-      <c r="N36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+      <c r="N36" s="17" t="n"/>
       <c r="O36" s="12" t="n"/>
       <c r="P36" s="12" t="n"/>
       <c r="Q36" s="12" t="n"/>
       <c r="R36" s="12" t="n"/>
       <c r="S36" s="13" t="inlineStr">
         <is>
-          <t>출퇴근 기록기 사번정보 변경</t>
+          <t>연동 결과 확인</t>
         </is>
       </c>
       <c r="T36" s="14" t="inlineStr">
         <is>
-          <t>11.02~11.13</t>
+          <t>11.16~11.20</t>
         </is>
       </c>
     </row>
     <row r="37" ht="19.9" customHeight="1" s="19">
-      <c r="A37" s="30" t="n"/>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>출퇴근기록기 테스트</t>
-        </is>
-      </c>
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>통합테스트 · 오픈</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>통합테스트 · 안정화</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="n"/>
       <c r="D37" s="12" t="n"/>
       <c r="E37" s="12" t="n"/>
       <c r="F37" s="12" t="n"/>
@@ -1859,34 +1842,26 @@
       <c r="K37" s="12" t="n"/>
       <c r="L37" s="12" t="n"/>
       <c r="M37" s="12" t="n"/>
-      <c r="N37" s="17" t="n"/>
-      <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="12" t="n"/>
-      <c r="R37" s="12" t="n"/>
-      <c r="S37" s="13" t="inlineStr">
-        <is>
-          <t>연동 결과 확인</t>
-        </is>
-      </c>
+      <c r="N37" s="11" t="n"/>
+      <c r="O37" s="11" t="n"/>
+      <c r="P37" s="11" t="n"/>
+      <c r="Q37" s="11" t="n"/>
+      <c r="R37" s="11" t="n"/>
+      <c r="S37" s="13" t="n"/>
       <c r="T37" s="14" t="inlineStr">
         <is>
-          <t>11.16~11.20</t>
+          <t>11.16~12.18</t>
         </is>
       </c>
     </row>
     <row r="38" ht="19.9" customHeight="1" s="19">
-      <c r="A38" s="22" t="inlineStr">
-        <is>
-          <t>통합테스트 · 오픈</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>통합테스트 · 안정화</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="n"/>
+      <c r="A38" s="27" t="n"/>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>통합테스트</t>
+        </is>
+      </c>
       <c r="D38" s="12" t="n"/>
       <c r="E38" s="12" t="n"/>
       <c r="F38" s="12" t="n"/>
@@ -1897,15 +1872,19 @@
       <c r="K38" s="12" t="n"/>
       <c r="L38" s="12" t="n"/>
       <c r="M38" s="12" t="n"/>
-      <c r="N38" s="11" t="n"/>
-      <c r="O38" s="11" t="n"/>
-      <c r="P38" s="11" t="n"/>
-      <c r="Q38" s="11" t="n"/>
-      <c r="R38" s="11" t="n"/>
-      <c r="S38" s="13" t="n"/>
+      <c r="N38" s="17" t="n"/>
+      <c r="O38" s="17" t="n"/>
+      <c r="P38" s="12" t="n"/>
+      <c r="Q38" s="12" t="n"/>
+      <c r="R38" s="12" t="n"/>
+      <c r="S38" s="13" t="inlineStr">
+        <is>
+          <t>검수 시나리오 작성 · 테스트 수행 · 검수확인서 날인</t>
+        </is>
+      </c>
       <c r="T38" s="14" t="inlineStr">
         <is>
-          <t>11.16~12.18</t>
+          <t>11.16~11.27</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1893,7 @@
       <c r="B39" s="12" t="n"/>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>통합테스트</t>
+          <t>시스템 오픈</t>
         </is>
       </c>
       <c r="D39" s="12" t="n"/>
@@ -1927,28 +1906,28 @@
       <c r="K39" s="12" t="n"/>
       <c r="L39" s="12" t="n"/>
       <c r="M39" s="12" t="n"/>
-      <c r="N39" s="17" t="n"/>
-      <c r="O39" s="17" t="n"/>
-      <c r="P39" s="12" t="n"/>
+      <c r="N39" s="12" t="n"/>
+      <c r="O39" s="12" t="n"/>
+      <c r="P39" s="16" t="n"/>
       <c r="Q39" s="12" t="n"/>
       <c r="R39" s="12" t="n"/>
       <c r="S39" s="13" t="inlineStr">
         <is>
-          <t>검수 시나리오 작성 · 테스트 수행 · 검수확인서 날인</t>
+          <t>임직원 공지 · 매뉴얼 배포</t>
         </is>
       </c>
       <c r="T39" s="14" t="inlineStr">
         <is>
-          <t>11.16~11.27</t>
+          <t>2026.11.30 오픈</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="27" t="n"/>
+      <c r="A40" s="30" t="n"/>
       <c r="B40" s="12" t="n"/>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>시스템 오픈</t>
+          <t>안정화 지원</t>
         </is>
       </c>
       <c r="D40" s="12" t="n"/>
@@ -1964,56 +1943,21 @@
       <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="16" t="n"/>
-      <c r="Q40" s="12" t="n"/>
-      <c r="R40" s="12" t="n"/>
+      <c r="Q40" s="16" t="n"/>
+      <c r="R40" s="16" t="n"/>
       <c r="S40" s="13" t="inlineStr">
         <is>
-          <t>임직원 공지 · 매뉴얼 배포</t>
+          <t>운영 이슈 접수 창구 운영</t>
         </is>
       </c>
       <c r="T40" s="14" t="inlineStr">
         <is>
-          <t>2026.11.30 오픈</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="30" t="n"/>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="15" t="inlineStr">
-        <is>
-          <t>안정화 지원</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n"/>
-      <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="12" t="n"/>
-      <c r="M41" s="12" t="n"/>
-      <c r="N41" s="12" t="n"/>
-      <c r="O41" s="12" t="n"/>
-      <c r="P41" s="16" t="n"/>
-      <c r="Q41" s="16" t="n"/>
-      <c r="R41" s="16" t="n"/>
-      <c r="S41" s="13" t="inlineStr">
-        <is>
-          <t>운영 이슈 접수 창구 운영</t>
-        </is>
-      </c>
-      <c r="T41" s="14" t="inlineStr">
-        <is>
           <t>12.01~12.18</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>* 상기 일정은 사업 수행과정에서 협의에 따라 조정될 수 있습니다.</t>
         </is>
@@ -2021,19 +1965,19 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="L9:P9"/>
+    <mergeCell ref="T9:T11"/>
     <mergeCell ref="S9:S11"/>
+    <mergeCell ref="A12:A14"/>
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="H9:K9"/>
+    <mergeCell ref="A18:A28"/>
     <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A29:A31"/>
     <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="A33:A37"/>
-    <mergeCell ref="A19:A29"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="L9:P9"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A32:A36"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A9:A11"/>
   </mergeCells>
